--- a/data/trans_dic/IP16A10-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea</t>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 20,25</t>
+          <t>3,62; 20,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,71</t>
+          <t>1,01; 9,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,54</t>
+          <t>0,0; 11,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 8,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,76</t>
+          <t>2,13; 11,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,09</t>
+          <t>0,87; 6,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 15,05</t>
+          <t>2,34; 14,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,82</t>
+          <t>0,0; 8,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 6,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,97</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 8,28</t>
+          <t>1,41; 7,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,57</t>
+          <t>0,46; 4,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,96</t>
+          <t>0,57; 5,51</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,19</t>
+          <t>0,0; 19,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,26</t>
+          <t>0,0; 9,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 8,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,93</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 11,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,45</t>
+          <t>1,81; 14,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,43</t>
+          <t>0,9; 7,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,49</t>
+          <t>2,76; 9,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,07</t>
+          <t>0,6; 4,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,97</t>
+          <t>0,34; 2,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,52</t>
+          <t>0,46; 4,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,6</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,3</t>
+          <t>0,44; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,59</t>
+          <t>2,03; 5,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,44</t>
+          <t>0,97; 3,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,56</t>
+          <t>0,43; 2,56</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2595</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1050; 6046</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>494; 4766</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3100</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3362</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4377</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1250; 6944</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>872; 6624</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3106</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2846</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1589</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3572</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2241</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1012; 6111</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5268</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3480</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3776</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3345</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1324; 7265</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>643; 6292</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>563; 5426</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4360</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2752</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4263</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4026</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3686</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4714</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4631</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>590; 4619</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3942</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>610; 5182</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3296</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3459; 11637</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1123; 7525</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>558; 4656</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>669; 6158</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1875; 8700</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>659; 5451</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5470; 14693</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3667; 13254</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1349; 7953</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A10-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Edad-trans_dic.xlsx
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 20,82</t>
+          <t>3,6; 19,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,76</t>
+          <t>1,04; 9,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,34</t>
+          <t>0,0; 11,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,56</t>
+          <t>0,0; 10,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 11,83</t>
+          <t>2,3; 11,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,63</t>
+          <t>0,64; 6,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 14,14</t>
+          <t>2,59; 13,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,07</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,71</t>
+          <t>1,31; 7,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,5</t>
+          <t>0,46; 4,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,51</t>
+          <t>0,56; 5,29</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,37</t>
+          <t>0,0; 18,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 10,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,96</t>
+          <t>0,0; 12,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,68</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,74</t>
+          <t>0,0; 11,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 14,18</t>
+          <t>1,85; 13,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,65</t>
+          <t>0,89; 8,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,29</t>
+          <t>2,85; 8,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,02</t>
+          <t>0,64; 3,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,86</t>
+          <t>0,34; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,28</t>
+          <t>0,47; 4,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,56</t>
+          <t>0,69; 4,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,68</t>
+          <t>0,44; 3,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,46</t>
+          <t>2,13; 5,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,51</t>
+          <t>1,01; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,56</t>
+          <t>0,45; 2,53</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1050; 6046</t>
+          <t>1045; 5721</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>494; 4766</t>
+          <t>506; 4679</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3100</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4377</t>
+          <t>0; 5261</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1250; 6944</t>
+          <t>1352; 6918</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>872; 6624</t>
+          <t>641; 6746</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>0; 3513</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1012; 6111</t>
+          <t>1117; 5798</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5268</t>
+          <t>0; 5204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3480</t>
+          <t>0; 3613</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3657</t>
+          <t>0; 3721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3776</t>
+          <t>0; 3306</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>0; 3357</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1324; 7265</t>
+          <t>1232; 7466</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>643; 6292</t>
+          <t>640; 5903</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>563; 5426</t>
+          <t>555; 5212</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4360</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1763,27 +1763,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2752</t>
+          <t>0; 3295</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4263</t>
+          <t>0; 5477</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4026</t>
+          <t>0; 4296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3686</t>
+          <t>0; 3654</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4714</t>
+          <t>0; 4756</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4631</t>
+          <t>0; 4465</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>590; 4619</t>
+          <t>601; 4544</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 4039</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>610; 5182</t>
+          <t>601; 5663</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3459; 11637</t>
+          <t>3573; 11072</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1123; 7525</t>
+          <t>1193; 7245</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558; 4656</t>
+          <t>557; 4794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>669; 6158</t>
+          <t>683; 6916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1875; 8700</t>
+          <t>1314; 8057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>659; 5451</t>
+          <t>656; 5618</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5470; 14693</t>
+          <t>5721; 14906</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3667; 13254</t>
+          <t>3803; 13004</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1349; 7953</t>
+          <t>1393; 7846</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A10-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A10-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,54%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 19,7</t>
+          <t>0,0; 11,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,58</t>
+          <t>0,0; 8,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,75</t>
+          <t>3,48; 20,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,29</t>
+          <t>1,01; 8,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 11,79</t>
+          <t>2,22; 11,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,75</t>
+          <t>0,62; 6,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 13,42</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,07</t>
+          <t>0,0; 7,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>2,39; 15,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 7,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,93</t>
+          <t>1,41; 8,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,22</t>
+          <t>0,46; 4,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,29</t>
+          <t>0,57; 4,96</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 10,17</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 11,26</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 17,19</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,14</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,8</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 4,93</t>
         </is>
       </c>
     </row>
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,29 +1008,29 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 10,21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1,82; 15,45</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,32</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 13,95</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,36</t>
+          <t>0,88; 7,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,84</t>
+          <t>0,46; 4,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,87</t>
+          <t>0,81; 4,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,95</t>
+          <t>0,45; 3,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,81</t>
+          <t>3,04; 9,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,22</t>
+          <t>0,65; 4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,79</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,54</t>
+          <t>2,13; 5,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,44</t>
+          <t>1,04; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,53</t>
+          <t>0,45; 2,56</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
+          <t>Menores que consumieron  medicamentos para la diarrea (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>2770</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1045; 5721</t>
+          <t>0; 3421</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>506; 4679</t>
+          <t>0; 4369</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>1010; 5880</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5261</t>
+          <t>493; 4255</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3440</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1352; 6918</t>
+          <t>1302; 6903</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>641; 6746</t>
+          <t>617; 6092</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3134</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2846</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1149</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1117; 5798</t>
+          <t>0; 3592</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5204</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3613</t>
+          <t>0; 3774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3721</t>
+          <t>1034; 6504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 5100</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3357</t>
+          <t>0; 4015</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1232; 7466</t>
+          <t>1330; 7795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>640; 5903</t>
+          <t>640; 6397</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>555; 5212</t>
+          <t>565; 4883</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1181</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4089</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 3305</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4819</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3295</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5477</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>0; 3926</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3654</t>
+          <t>0; 3285</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4756</t>
+          <t>0; 4277</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,29 +1906,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 4027</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>593; 5030</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4465</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>601; 4544</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4039</t>
+          <t>0; 4012</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>601; 5663</t>
+          <t>596; 5031</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1762</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3573; 11072</t>
+          <t>669; 6504</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1193; 7245</t>
+          <t>1547; 8784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>557; 4794</t>
+          <t>661; 4881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>683; 6916</t>
+          <t>3809; 11888</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1314; 8057</t>
+          <t>1211; 7613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>656; 5618</t>
+          <t>554; 4830</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5721; 14906</t>
+          <t>5723; 15037</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3803; 13004</t>
+          <t>3915; 12980</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1393; 7846</t>
+          <t>1392; 7948</t>
         </is>
       </c>
     </row>
